--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -726,7 +726,7 @@
   </si>
   <si>
     <t>Les codes FINEJ, FINEG, SIREN, SIRET, IDNST, INTRN proviennent de la terminologie  http://interopsante.org/CodeSystem/fr-v2-0203 
- Les codes 0,4 proviennent de la terminologie TRE-G07-TypeIdentifiantStructure.</t>
+ Les codes 0,4 proviennent de la terminologie JDV_J104-TypeIdentifiantStructure-RASS.</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -9640,7 +9640,7 @@
         <v>72</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>71</v>
@@ -9744,7 +9744,7 @@
         <v>72</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>71</v>
@@ -9848,7 +9848,7 @@
         <v>72</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>71</v>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
